--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-26.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -700,6 +700,88 @@
       </c>
       <c r="T3" t="n">
         <v>34.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Flamengo x Atletico MG</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Atletico MG</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>3745</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>200</v>
+      </c>
+      <c r="S4" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="T4" t="n">
+        <v>31.83</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-26.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-26.xlsx
@@ -750,15 +750,19 @@
       <c r="K4" t="n">
         <v>1.27</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
